--- a/data/trans_camb/IP18A03-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP18A03-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-3.766130586681138</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>12.21081519949168</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.911533984743986</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.8877078336174349</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.5400504289822416</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>6.670975909879751</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-10.63383487160614</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.681314511710271</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.195217445683979</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-24.39302209059847</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-5.603960584262349</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-8.378712293503385</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>3.271294327218322</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>24.39027167068257</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.89881137291666</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>17.2646972262388</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>4.253392512610511</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>17.18005567442302</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.05382394136586961</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.174511792992842</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.04348532409839743</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.01325839335958662</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.007884646854625931</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.097395143865071</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.1484897210045327</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.03442331814499312</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.0449697403393244</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.3593664421505708</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.07880617496967429</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1139955233968176</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.04862573098306634</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.3571894297727389</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.176414701469337</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.2622602710592792</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.06363110658284674</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.2524980545071224</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-6.84961171186057</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>8.90768159642813</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-5.018624556393892</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>17.380124603717</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-5.982784583126421</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>12.65948611894151</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-14.74181345331404</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.431573130120848</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-12.67465397450155</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>3.319143678519453</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-11.82064870962915</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>3.741846458335176</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>1.027042576948857</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>18.9483566157189</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.639796645053588</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>28.70424939539103</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-0.2195868655407602</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>20.50790816771889</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.09690774682217509</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.1260251513855122</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.07559737052388578</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.261803150376044</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.08727242862792303</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1846672036124285</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.1991777670684056</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.06000207772924409</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.1836022447159466</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.05320079489026919</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.167281832648062</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.05331301603213089</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.01687475396155651</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.2807453478667399</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.05974886305431915</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.4559104093232351</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.003121010406916919</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.3084548460652238</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>1.828355349180655</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>20.3576931452196</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.207707804194447</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.074868835174715</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1.609982548559652</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>12.45191400542682</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-8.721164936610931</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>5.513567434910324</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-7.745212790381895</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-15.44521831170822</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-4.868230244095975</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1.744983440577085</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>11.39517477849254</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>32.22040169494788</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>10.31019562757117</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>18.01598449810617</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>8.237842171061461</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>22.43473765167988</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.03174901030075773</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.3535071066228381</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.01963331777968408</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.03373047607266214</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.02705532084127111</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.2092510436253699</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.1386528940764882</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.09659638712988126</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.1215704932361221</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.2388848654511629</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.07704122263383802</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.02771227388433824</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.21775866707542</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.602017412816181</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.1847125836680528</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.3113246667833859</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.1449372067522379</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.3901071329394654</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>11.48879791362324</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>19.31019336626967</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.381084789945164</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>25.13204843489324</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>7.059138271751831</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>22.29375417090233</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>0.6512272746743075</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.5018149133311836</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-12.5662967955375</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>8.580105699785131</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-2.574913667891667</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>8.849692525112721</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>22.82227526814525</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>33.81663286184094</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>15.01192104737878</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>38.2993640148993</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>15.28219557358836</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>32.71404718952022</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>0.1977407227989056</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.3323595403401589</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.02264205710419346</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.4120248662146243</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.1188470458720607</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.3753357311631393</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>0.006666502201570168</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.002623902789907084</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.1867060210824746</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0.1369794982529912</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.04079365861120069</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0.1427647598056473</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.428609921903388</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.6489145290370136</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.2718662165073337</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.7384732132674885</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.2750634002951426</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.5980131481486712</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-1.190213929132578</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>13.11854277762852</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.1470221476349898</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>9.904275015137376</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.5389226938715908</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>11.80383545052436</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-5.647601217249511</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>6.1831195888516</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-4.130725363892806</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.7306367016316695</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-3.472145591412237</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>6.113090415427639</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>3.241925984209131</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>19.26375779653179</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>4.899446679774433</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>17.62912619276505</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>2.454599418220552</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>17.04115063624993</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.01807385744885252</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.1992101304614465</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.002266591693946907</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.1526909234084242</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.008243871255005085</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.1805626314793373</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.08419862868203448</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.09236555690778195</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.06196635690661949</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>0.01330346354039544</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.05236354768301289</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>0.09053568307702238</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.05061114346995951</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.3038307696726342</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.07814323633845174</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.2806032232456778</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.03832943130619151</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.2636415475113507</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
